--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G1_task072.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G1_task072.xlsx
@@ -100,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
@@ -559,6 +559,50 @@
         <v>4.1025551861898082</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>549</v>
+      </c>
+      <c r="B11" s="0">
+        <v>720</v>
+      </c>
+      <c r="C11" s="0">
+        <v>549</v>
+      </c>
+      <c r="D11" s="0">
+        <v>93.184339810505861</v>
+      </c>
+      <c r="E11" s="0">
+        <v>531.84500000000003</v>
+      </c>
+      <c r="F11" s="0">
+        <v>138.48318997741234</v>
+      </c>
+      <c r="G11" s="0">
+        <v>6642.0880828816089</v>
+      </c>
+      <c r="H11" s="0">
+        <v>-937.65961786081266</v>
+      </c>
+      <c r="I11" s="0">
+        <v>7.2450000000000001</v>
+      </c>
+      <c r="J11" s="0">
+        <v>36.555</v>
+      </c>
+      <c r="K11" s="0">
+        <v>4.7199999999999998</v>
+      </c>
+      <c r="L11" s="0">
+        <v>6.254999999999999</v>
+      </c>
+      <c r="M11" s="0">
+        <v>221.48397432509054</v>
+      </c>
+      <c r="N11" s="0">
+        <v>4.1025551861898082</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>